--- a/output/pdf_financials_xlsx/AAAJ.P.xlsx
+++ b/output/pdf_financials_xlsx/AAAJ.P.xlsx
@@ -2525,16 +2525,16 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.062472</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.062472</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.062472</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.062472</v>
       </c>
     </row>
     <row r="93">
@@ -3844,7 +3844,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -4497,7 +4501,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AAAJ.P.xlsx
+++ b/output/pdf_financials_xlsx/AAAJ.P.xlsx
@@ -631,13 +631,13 @@
         <v>0.016049</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.015317</v>
+        <v>0.064759</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.017994</v>
+        <v>0.059036</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.018026</v>
+        <v>0.045521</v>
       </c>
     </row>
     <row r="11">
@@ -653,13 +653,13 @@
         <v>-0.016049</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.015317</v>
+        <v>-0.064759</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.017994</v>
+        <v>-0.059036</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.018026</v>
+        <v>-0.045521</v>
       </c>
     </row>
     <row r="12">
@@ -678,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.008872</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004338</v>
       </c>
     </row>
     <row r="13">
@@ -1036,10 +1036,10 @@
         <v>-0.064759</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.050164</v>
+        <v>-0.059036</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.031109</v>
+        <v>-0.035447</v>
       </c>
     </row>
     <row r="28">
@@ -1080,10 +1080,10 @@
         <v>-0.064759</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.050164</v>
+        <v>-0.059036</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.031109</v>
+        <v>-0.035447</v>
       </c>
     </row>
     <row r="30">
@@ -1189,16 +1189,16 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.376315</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.24715</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.197705</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.154662</v>
       </c>
     </row>
     <row r="35">
@@ -1233,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.376315</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.24715</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.197705</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.154662</v>
       </c>
     </row>
     <row r="37">
@@ -1497,16 +1497,16 @@
         <v>0.228481</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.376315</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.25009</v>
+        <v>0.00294</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.200645</v>
+        <v>0.00294</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.157563</v>
+        <v>0.002901</v>
       </c>
     </row>
     <row r="49">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7041,13 +7041,13 @@
         </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-0.064759</v>
+        <v>0.064759</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>-0.059036</v>
+        <v>0.059036</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>-0.045521</v>
+        <v>0.045521</v>
       </c>
     </row>
     <row r="89">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">

--- a/output/pdf_financials_xlsx/AAAJ.P.xlsx
+++ b/output/pdf_financials_xlsx/AAAJ.P.xlsx
@@ -6469,7 +6469,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
         <v>0.235</v>
       </c>
